--- a/Scout_Evolution_Saison.xlsx
+++ b/Scout_Evolution_Saison.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
@@ -155,7 +150,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -490,7 +485,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E106"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2302,7 +2304,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -2344,7 +2346,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
